--- a/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>MARX</t>
   </si>
@@ -656,67 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -750,8 +757,14 @@
       <c r="M8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -785,8 +798,14 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -820,8 +839,14 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -835,8 +860,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -870,8 +897,14 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,8 +938,14 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -940,8 +979,14 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -975,8 +1020,14 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -987,34 +1038,36 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>100</v>
+      </c>
+      <c r="E17" s="3">
+        <v>100</v>
+      </c>
+      <c r="F17" s="3">
         <v>200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>200</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
       <c r="H17" s="3">
         <v>0</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
@@ -1022,8 +1075,14 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1031,13 +1090,13 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H18" s="3">
         <v>0</v>
@@ -1045,11 +1104,11 @@
       <c r="I18" s="3">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
@@ -1057,8 +1116,14 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1072,8 +1137,10 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1081,25 +1148,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>900</v>
+      </c>
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
@@ -1107,8 +1174,14 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1142,8 +1215,14 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,34 +1256,40 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>800</v>
+      </c>
+      <c r="F23" s="3">
         <v>700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
         <v>0</v>
       </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
@@ -1212,8 +1297,14 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1247,8 +1338,14 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1282,34 +1379,40 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>800</v>
+      </c>
+      <c r="F26" s="3">
         <v>700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
         <v>0</v>
       </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
@@ -1317,34 +1420,40 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>800</v>
+      </c>
+      <c r="F27" s="3">
         <v>700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
         <v>0</v>
       </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
@@ -1352,8 +1461,14 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1387,8 +1502,14 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1422,8 +1543,14 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1457,8 +1584,14 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1492,8 +1625,14 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1501,25 +1640,25 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
@@ -1527,34 +1666,40 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>800</v>
+      </c>
+      <c r="F33" s="3">
         <v>700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
         <v>0</v>
       </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
@@ -1562,8 +1707,14 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1597,34 +1748,40 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>800</v>
+      </c>
+      <c r="F35" s="3">
         <v>700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
         <v>0</v>
       </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
@@ -1632,48 +1789,60 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1687,8 +1856,10 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1702,58 +1873,66 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
+        <v>200</v>
+      </c>
+      <c r="G41" s="3">
         <v>400</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
         <v>0</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3">
+        <v>0</v>
+      </c>
+      <c r="O41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E42" s="3">
+        <v>72600</v>
+      </c>
+      <c r="F42" s="3">
         <v>71600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>70800</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1763,17 +1942,23 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1807,8 +1992,14 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1842,32 +2033,38 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,32 +2074,38 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>72900</v>
+      </c>
+      <c r="F46" s="3">
         <v>72100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>71400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1912,8 +2115,14 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1947,8 +2156,14 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1982,8 +2197,14 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2017,8 +2238,14 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2052,8 +2279,14 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2087,8 +2320,14 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2122,8 +2361,14 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2157,32 +2402,38 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>72900</v>
+      </c>
+      <c r="F54" s="3">
         <v>72100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>71400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>100</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,8 +2443,14 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2207,8 +2464,10 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2222,8 +2481,10 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2257,32 +2518,38 @@
       <c r="M57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2292,8 +2559,14 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2301,22 +2574,22 @@
         <v>0</v>
       </c>
       <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2327,8 +2600,14 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2336,23 +2615,23 @@
         <v>0</v>
       </c>
       <c r="E60" s="3">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3">
+        <v>0</v>
+      </c>
+      <c r="G60" s="3">
         <v>100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2362,8 +2641,14 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2397,8 +2682,14 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2432,8 +2723,14 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2467,8 +2764,14 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2502,8 +2805,14 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2537,8 +2846,14 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -2546,23 +2861,23 @@
         <v>0</v>
       </c>
       <c r="E66" s="3">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3">
+        <v>0</v>
+      </c>
+      <c r="G66" s="3">
         <v>100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2887,14 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2587,8 +2908,10 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2622,8 +2945,14 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2657,8 +2986,14 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2692,8 +3027,14 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2727,31 +3068,37 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>300</v>
+      </c>
+      <c r="F72" s="3">
         <v>400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-100</v>
       </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>0</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2762,8 +3109,14 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2797,8 +3150,14 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2832,8 +3191,14 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2867,31 +3232,37 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>73800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>72900</v>
+      </c>
+      <c r="F76" s="3">
         <v>72100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>71400</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="3">
-        <v>0</v>
-      </c>
       <c r="H76" s="3">
         <v>0</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2902,8 +3273,14 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2937,74 +3314,86 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>800</v>
+      </c>
+      <c r="F81" s="3">
         <v>700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
         <v>0</v>
       </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
       </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
@@ -3012,8 +3401,14 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3027,8 +3422,10 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3062,8 +3459,14 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3097,8 +3500,14 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3132,8 +3541,14 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3167,8 +3582,14 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3202,8 +3623,14 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3237,43 +3664,55 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-400</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
         <v>0</v>
       </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3287,8 +3726,10 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3322,8 +3763,14 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3357,8 +3804,14 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3392,8 +3845,14 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3427,8 +3886,14 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3442,8 +3907,10 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3477,8 +3944,14 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3512,8 +3985,14 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3547,8 +4026,14 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3582,43 +4067,55 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>71200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3652,39 +4149,51 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>MARX</t>
   </si>
@@ -656,63 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -722,8 +723,11 @@
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -763,8 +767,11 @@
       <c r="O8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -804,8 +811,11 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -845,8 +855,11 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,8 +875,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -903,8 +917,11 @@
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +961,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,8 +1005,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1026,8 +1049,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,8 +1066,9 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1052,13 +1079,13 @@
         <v>100</v>
       </c>
       <c r="F17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3">
         <v>200</v>
       </c>
       <c r="H17" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I17" s="3">
         <v>0</v>
@@ -1069,8 +1096,8 @@
       <c r="K17" s="3">
         <v>0</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
+      <c r="L17" s="3">
+        <v>0</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
@@ -1081,8 +1108,11 @@
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1093,13 +1123,13 @@
         <v>-100</v>
       </c>
       <c r="F18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G18" s="3">
         <v>-200</v>
       </c>
       <c r="H18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I18" s="3">
         <v>0</v>
@@ -1110,8 +1140,8 @@
       <c r="K18" s="3">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
+      <c r="L18" s="3">
+        <v>0</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
@@ -1122,8 +1152,11 @@
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,8 +1172,9 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1151,14 +1185,14 @@
         <v>1000</v>
       </c>
       <c r="F20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="3">
         <v>900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1168,8 +1202,8 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1180,8 +1214,11 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1221,8 +1258,11 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,26 +1302,29 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>100</v>
+      </c>
+      <c r="E23" s="3">
         <v>900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
         <v>0</v>
       </c>
@@ -1291,8 +1334,8 @@
       <c r="K23" s="3">
         <v>0</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
+      <c r="L23" s="3">
+        <v>0</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
@@ -1303,8 +1346,11 @@
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1344,8 +1390,11 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,26 +1434,29 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
         <v>900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
         <v>0</v>
       </c>
@@ -1414,8 +1466,8 @@
       <c r="K26" s="3">
         <v>0</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="3">
+        <v>0</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
@@ -1426,26 +1478,29 @@
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>100</v>
+      </c>
+      <c r="E27" s="3">
         <v>900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
         <v>0</v>
       </c>
@@ -1455,8 +1510,8 @@
       <c r="K27" s="3">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
+      <c r="L27" s="3">
+        <v>0</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
@@ -1467,8 +1522,11 @@
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,8 +1698,11 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1643,14 +1713,14 @@
         <v>-1000</v>
       </c>
       <c r="F32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1660,8 +1730,8 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1672,26 +1742,29 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
         <v>900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
         <v>0</v>
       </c>
@@ -1701,8 +1774,8 @@
       <c r="K33" s="3">
         <v>0</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
+      <c r="L33" s="3">
+        <v>0</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
@@ -1713,8 +1786,11 @@
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,26 +1830,29 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>100</v>
+      </c>
+      <c r="E35" s="3">
         <v>900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
         <v>0</v>
       </c>
@@ -1783,8 +1862,8 @@
       <c r="K35" s="3">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
+      <c r="L35" s="3">
+        <v>0</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
@@ -1795,43 +1874,46 @@
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1841,8 +1923,11 @@
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,40 +1961,41 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
-      </c>
-      <c r="E41" s="3">
-        <v>200</v>
       </c>
       <c r="F41" s="3">
         <v>200</v>
       </c>
       <c r="G41" s="3">
+        <v>200</v>
+      </c>
+      <c r="H41" s="3">
         <v>400</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
         <v>0</v>
       </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
+      <c r="K41" s="3">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3">
-        <v>0</v>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -1916,26 +2003,29 @@
       <c r="O41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E42" s="3">
         <v>73600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>72600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>71600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>70800</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1948,8 +2038,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -1957,8 +2047,11 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1998,8 +2091,11 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2039,8 +2135,11 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2051,23 +2150,23 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
       </c>
       <c r="I45" s="3">
         <v>200</v>
       </c>
       <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,35 +2179,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E46" s="3">
         <v>73800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>72900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>200</v>
       </c>
       <c r="I46" s="3">
         <v>200</v>
       </c>
       <c r="J46" s="3">
+        <v>200</v>
+      </c>
+      <c r="K46" s="3">
         <v>100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2121,8 +2223,11 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2162,8 +2267,11 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2203,8 +2311,11 @@
       <c r="O48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2244,8 +2355,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,8 +2443,11 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2367,8 +2487,11 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,35 +2531,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E54" s="3">
         <v>73800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>72900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71400</v>
-      </c>
-      <c r="H54" s="3">
-        <v>200</v>
       </c>
       <c r="I54" s="3">
         <v>200</v>
       </c>
       <c r="J54" s="3">
+        <v>200</v>
+      </c>
+      <c r="K54" s="3">
         <v>100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,8 +2575,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,8 +2613,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2524,16 +2655,19 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2542,16 +2676,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>200</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2565,13 +2699,16 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E59" s="3">
         <v>0</v>
@@ -2580,19 +2717,19 @@
         <v>0</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J59" s="3">
         <v>0</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
+      <c r="K59" s="3">
+        <v>0</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
@@ -2606,13 +2743,16 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E60" s="3">
         <v>0</v>
@@ -2621,19 +2761,19 @@
         <v>0</v>
       </c>
       <c r="G60" s="3">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3">
         <v>100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>200</v>
       </c>
       <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
+      <c r="K60" s="3">
+        <v>200</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
@@ -2647,8 +2787,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2688,8 +2831,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2729,8 +2875,11 @@
       <c r="O62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,13 +3007,16 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E66" s="3">
         <v>0</v>
@@ -2867,19 +3025,19 @@
         <v>0</v>
       </c>
       <c r="G66" s="3">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3">
         <v>100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>200</v>
       </c>
       <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
+      <c r="K66" s="3">
+        <v>200</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
@@ -2893,8 +3051,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,34 +3245,37 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E72" s="3">
         <v>200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>100</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-100</v>
       </c>
       <c r="I72" s="3">
         <v>-100</v>
       </c>
       <c r="J72" s="3">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="K72" s="3">
+        <v>0</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
@@ -3115,8 +3289,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,34 +3421,37 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E76" s="3">
         <v>73800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71400</v>
       </c>
-      <c r="H76" s="3">
-        <v>0</v>
-      </c>
       <c r="I76" s="3">
         <v>0</v>
       </c>
       <c r="J76" s="3">
         <v>0</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
+      <c r="K76" s="3">
+        <v>0</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
@@ -3279,8 +3465,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,43 +3509,46 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,26 +3558,29 @@
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>100</v>
+      </c>
+      <c r="E81" s="3">
         <v>900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
         <v>0</v>
       </c>
@@ -3395,8 +3590,8 @@
       <c r="K81" s="3">
         <v>0</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
+      <c r="L81" s="3">
+        <v>0</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
@@ -3407,8 +3602,11 @@
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,8 +3622,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3465,8 +3664,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,8 +3884,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3679,17 +3896,17 @@
         <v>0</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
         <v>0</v>
       </c>
@@ -3699,11 +3916,11 @@
       <c r="K89" s="3">
         <v>0</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -3711,8 +3928,11 @@
       <c r="O89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,8 +3948,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3769,8 +3990,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,8 +4078,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3892,8 +4122,11 @@
       <c r="O94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4184,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,26 +4316,29 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>71200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -4102,11 +4348,11 @@
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -4114,8 +4360,11 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4155,26 +4404,29 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>400</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
@@ -4184,16 +4436,19 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MARX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>MARX</t>
   </si>
@@ -656,67 +656,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,8 +727,11 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -770,8 +774,11 @@
       <c r="P8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -814,8 +821,11 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -858,8 +868,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +889,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +934,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1075,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,13 +1093,14 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E17" s="3">
         <v>100</v>
@@ -1082,13 +1109,13 @@
         <v>100</v>
       </c>
       <c r="G17" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H17" s="3">
         <v>200</v>
       </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J17" s="3">
         <v>0</v>
@@ -1099,8 +1126,8 @@
       <c r="L17" s="3">
         <v>0</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
+      <c r="M17" s="3">
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
@@ -1111,8 +1138,11 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1126,13 +1156,13 @@
         <v>-100</v>
       </c>
       <c r="G18" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H18" s="3">
         <v>-200</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J18" s="3">
         <v>0</v>
@@ -1143,8 +1173,8 @@
       <c r="L18" s="3">
         <v>0</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
+      <c r="M18" s="3">
+        <v>0</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
@@ -1155,8 +1185,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,8 +1206,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,20 +1216,20 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
         <v>1000</v>
       </c>
       <c r="G20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1205,8 +1239,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1217,8 +1251,11 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1261,8 +1298,11 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1305,29 +1345,32 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>100</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1380,8 @@
       <c r="L23" s="3">
         <v>0</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>0</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
@@ -1349,8 +1392,11 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,29 +1486,32 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
         <v>100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>100</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
         <v>0</v>
       </c>
@@ -1469,8 +1521,8 @@
       <c r="L26" s="3">
         <v>0</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>0</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
@@ -1481,29 +1533,32 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
         <v>100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>100</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
         <v>0</v>
       </c>
@@ -1513,8 +1568,8 @@
       <c r="L27" s="3">
         <v>0</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>0</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
@@ -1525,8 +1580,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,8 +1768,11 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1710,20 +1780,20 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
         <v>-1000</v>
       </c>
       <c r="G32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -1733,8 +1803,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1745,29 +1815,32 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
         <v>100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>100</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
         <v>0</v>
       </c>
@@ -1777,8 +1850,8 @@
       <c r="L33" s="3">
         <v>0</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>0</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
@@ -1789,8 +1862,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,29 +1909,32 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
         <v>100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>100</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
         <v>0</v>
       </c>
@@ -1865,8 +1944,8 @@
       <c r="L35" s="3">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>0</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
@@ -1877,46 +1956,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2008,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,43 +2048,44 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>200</v>
       </c>
       <c r="G41" s="3">
         <v>200</v>
       </c>
       <c r="H41" s="3">
+        <v>200</v>
+      </c>
+      <c r="I41" s="3">
         <v>400</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
         <v>0</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
+      <c r="N41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
@@ -2006,29 +2093,32 @@
       <c r="P41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E42" s="3">
         <v>22500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>73600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>72600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>71600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>70800</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,8 +2131,8 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2094,8 +2187,11 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,8 +2234,11 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2153,23 +2252,23 @@
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
       <c r="K45" s="3">
+        <v>200</v>
+      </c>
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,38 +2281,41 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E46" s="3">
         <v>22900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>73800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>72900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>71400</v>
-      </c>
-      <c r="I46" s="3">
-        <v>200</v>
       </c>
       <c r="J46" s="3">
         <v>200</v>
       </c>
       <c r="K46" s="3">
+        <v>200</v>
+      </c>
+      <c r="L46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,8 +2328,11 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2270,8 +2375,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2563,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,38 +2657,41 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E54" s="3">
         <v>22900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>73800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>72900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>72100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71400</v>
-      </c>
-      <c r="I54" s="3">
-        <v>200</v>
       </c>
       <c r="J54" s="3">
         <v>200</v>
       </c>
       <c r="K54" s="3">
+        <v>200</v>
+      </c>
+      <c r="L54" s="3">
         <v>100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,8 +2744,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2658,19 +2789,22 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
@@ -2679,16 +2813,16 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>300</v>
-      </c>
-      <c r="J58" s="3">
-        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>200</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2702,17 +2836,20 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
@@ -2720,19 +2857,19 @@
         <v>0</v>
       </c>
       <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2746,17 +2883,20 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>900</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
       <c r="F60" s="3">
         <v>0</v>
       </c>
@@ -2764,19 +2904,19 @@
         <v>0</v>
       </c>
       <c r="H60" s="3">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3">
         <v>100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>200</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
+      <c r="L60" s="3">
+        <v>200</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
@@ -2790,8 +2930,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2834,8 +2977,11 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,17 +3165,20 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>900</v>
+      </c>
+      <c r="E66" s="3">
         <v>600</v>
       </c>
-      <c r="E66" s="3">
-        <v>0</v>
-      </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
@@ -3028,19 +3186,19 @@
         <v>0</v>
       </c>
       <c r="H66" s="3">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3">
         <v>100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>300</v>
-      </c>
-      <c r="J66" s="3">
-        <v>200</v>
       </c>
       <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
+      <c r="L66" s="3">
+        <v>200</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,37 +3419,40 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-100</v>
       </c>
       <c r="J72" s="3">
         <v>-100</v>
       </c>
       <c r="K72" s="3">
-        <v>0</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="L72" s="3">
+        <v>0</v>
       </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,37 +3607,40 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E76" s="3">
         <v>22300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>73800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>72100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>71400</v>
       </c>
-      <c r="I76" s="3">
-        <v>0</v>
-      </c>
       <c r="J76" s="3">
         <v>0</v>
       </c>
       <c r="K76" s="3">
         <v>0</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
+      <c r="L76" s="3">
+        <v>0</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,46 +3701,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,29 +3753,32 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
         <v>100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>100</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
         <v>0</v>
       </c>
@@ -3593,8 +3788,8 @@
       <c r="L81" s="3">
         <v>0</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>0</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
@@ -3605,8 +3800,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,8 +3821,9 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3667,8 +3866,11 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,29 +4101,32 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E89" s="3">
         <v>0</v>
       </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-400</v>
       </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
       <c r="J89" s="3">
         <v>0</v>
       </c>
@@ -3919,11 +4136,11 @@
       <c r="L89" s="3">
         <v>0</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -3931,8 +4148,11 @@
       <c r="P89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4169,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,8 +4308,11 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4125,8 +4355,11 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,29 +4562,32 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>100</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>71200</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -4351,11 +4597,11 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -4363,8 +4609,11 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,29 +4656,32 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -4439,16 +4691,19 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
       </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>0</v>
       </c>
     </row>
